--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -102,7 +102,8 @@
 Atlas 350 加速卡
 Atlas 850E 超节点
 Atlas 650E 服务器
-Atlas 950 SuperPoD 超节点</t>
+Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <t>nodeBase</t>
@@ -326,7 +327,8 @@
     <t>Atlas 350 加速卡（4Pmesh互联）
 Atlas 850E 超节点
 Atlas 650E 服务器
-Atlas 950 SuperPoD 超节点</t>
+Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <r>
@@ -672,6 +674,7 @@
 Atlas 850E 超节点
 Atlas 650E 服务器
 Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex
 说明：
 只有Atlas 推理系列产品为板卡功耗，其余产品为</t>
     </r>
@@ -767,7 +770,8 @@
 Atlas 350 加速卡
 Atlas 850E 超节点
 Atlas 650E 服务器
-Atlas 950 SuperPoD 超节点</t>
+Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <t>container_npu_used_memory</t>
@@ -868,7 +872,8 @@
 Atlas 350 加速卡
 Atlas 850E 超节点
 Atlas 650E 服务器
-Atlas 950 SuperPoD 超节点</t>
+Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <t>npu_chip_info_vector_utilization</t>
@@ -903,7 +908,8 @@
 Atlas 350 加速卡
 Atlas 850E 超节点
 Atlas 650E 服务器
-Atlas 950 SuperPoD 超节点</t>
+Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <t>RoCE</t>
@@ -992,7 +998,8 @@
 Atlas 350 加速卡
 Atlas 850E 超节点
 Atlas 650E 服务器
-Atlas 950 SuperPoD 超节点</t>
+Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_total_memory</t>
@@ -1346,7 +1353,8 @@
 Atlas 350 加速卡
 Atlas 850E 超节点
 Atlas 650E 服务器
-Atlas 950 SuperPoD 超节点</t>
+Atlas 950 SuperPoD 超节点
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <t>npu_chip_info_sio_crc_rx_err_cnt</t>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\go_project\mindCluster_gitcode\gitcode_mind-cluster_master2\docs\zh\resource\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="511">
   <si>
     <t>类别</t>
   </si>
@@ -90,13 +95,13 @@
 dcmiVersion：DCMI版本信息。字段类型为string。</t>
   </si>
   <si>
-    <t>Network</t>
-  </si>
-  <si>
-    <t>npu_chip_link_speed</t>
-  </si>
-  <si>
-    <t>网口默认速率</t>
+    <t>network_bandwidth</t>
+  </si>
+  <si>
+    <t>npu_chip_info_bandwidth_rx</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器网口实时接收速率</t>
   </si>
   <si>
     <t>详见“标签数据信息说明”页签中“标签1”</t>
@@ -112,25 +117,63 @@
 A200I A2 Box 异构组件</t>
   </si>
   <si>
-    <t>npu_chip_link_up_num</t>
-  </si>
-  <si>
-    <t>网口up的统计次数</t>
-  </si>
-  <si>
-    <t>单位：次</t>
-  </si>
-  <si>
-    <t>npu_chip_info_bandwidth_rx</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器网口实时接收速率</t>
-  </si>
-  <si>
     <t>npu_chip_info_bandwidth_tx</t>
   </si>
   <si>
     <t>昇腾AI处理器网口实时发送速率</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器端口实时接收速率。使用的-time参数为100。</t>
+  </si>
+  <si>
+    <t>详见“标签数据信息说明”页签中“标签8”</t>
+  </si>
+  <si>
+    <t>Ascend 950PR&amp;950DT系列产品
+说明：Atlas 350 加速卡仅支持4Pmesh互联</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器端口实时发送速率。使用的-time参数为100。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_bandwidth_rx_X_Y</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID。使用的-time参数为100。</t>
+  </si>
+  <si>
+    <t>Atlas 350 加速卡（4Pmesh互联）
+说明：旧版本指标</t>
+  </si>
+  <si>
+    <t>npu_chip_info_bandwidth_tx_X_Y</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID。使用的-time参数为100。</t>
+  </si>
+  <si>
+    <t>network_link</t>
+  </si>
+  <si>
+    <t>npu_chip_link_speed</t>
+  </si>
+  <si>
+    <t>网口默认速率</t>
+  </si>
+  <si>
+    <t>npu_chip_info_link_speed</t>
+  </si>
+  <si>
+    <t>物理端口的速率。</t>
+  </si>
+  <si>
+    <t>单位：G</t>
+  </si>
+  <si>
+    <t>npu_chip_info_link_speed_X_Y</t>
+  </si>
+  <si>
+    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID。</t>
   </si>
   <si>
     <t>npu_chip_info_link_status</t>
@@ -145,57 +188,22 @@
 • -1：未知(hccn_tool工具调用失败)</t>
   </si>
   <si>
+    <t>昇腾AI处理器端口Link状态。</t>
+  </si>
+  <si>
     <t>npu_chip_info_link_status_X_Y</t>
   </si>
   <si>
     <t>昇腾AI处理器端口Link状态。其中，X为Udie ID，Y为Port ID。</t>
   </si>
   <si>
-    <t>Atlas 350 加速卡（4Pmesh互联）
-说明：旧版本指标</t>
-  </si>
-  <si>
-    <t>npu_chip_info_bandwidth_rx_X_Y</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID。使用的-time参数为100。</t>
-  </si>
-  <si>
-    <t>npu_chip_info_bandwidth_tx_X_Y</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID。使用的-time参数为100。</t>
-  </si>
-  <si>
-    <t>npu_chip_info_link_speed_X_Y</t>
-  </si>
-  <si>
-    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID。</t>
-  </si>
-  <si>
-    <t>单位：G</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器端口Link状态。</t>
-  </si>
-  <si>
-    <t>详见“标签数据信息说明”页签中“标签8”</t>
-  </si>
-  <si>
-    <t>Ascend 950PR&amp;950DT系列产品
-说明：Atlas 350 加速卡仅支持4Pmesh互联</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器端口实时接收速率。使用的-time参数为100。</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器端口实时发送速率。使用的-time参数为100。</t>
-  </si>
-  <si>
-    <t>npu_chip_info_link_speed</t>
-  </si>
-  <si>
-    <t>物理端口的速率。</t>
+    <t>npu_chip_link_up_num</t>
+  </si>
+  <si>
+    <t>网口up的统计次数</t>
+  </si>
+  <si>
+    <t>单位：次</t>
   </si>
   <si>
     <t>NPU</t>
@@ -299,6 +307,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t>Atlas 训练系列产品
 Atlas A2 训练系列产品
 Atlas A3 训练系列产品
@@ -1601,6 +1615,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t>model_name：</t>
     </r>
     <r>
@@ -2434,7 +2454,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2454,9 +2474,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2465,22 +2482,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2805,11 +2819,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.25" style="4" customWidth="1"/>
+    <col min="1" max="1" width="18.8888888888889" style="4" customWidth="1"/>
     <col min="2" max="2" width="42" style="4" customWidth="1"/>
-    <col min="3" max="3" width="32.6333333333333" style="4" customWidth="1"/>
+    <col min="3" max="3" width="32.6296296296296" style="4" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="4" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="4" customWidth="1"/>
@@ -2817,22 +2831,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="69" customHeight="1" spans="1:6">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2876,169 +2890,169 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="81" customHeight="1" spans="1:6">
-      <c r="A4" s="11" t="s">
+    <row r="4" ht="82" customHeight="1" spans="1:6">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:6">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="82" customHeight="1" spans="1:6">
+    <row r="6" ht="69" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="78" customHeight="1" spans="1:6">
+      <c r="F6" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="71" customHeight="1" spans="1:6">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>28</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="84" customHeight="1" spans="1:6">
+      <c r="F7" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1" spans="1:6">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" ht="84" customHeight="1" spans="1:6">
+    </row>
+    <row r="9" ht="40.5" customHeight="1" spans="1:6">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="81" customHeight="1" spans="1:6">
+      <c r="A10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" ht="40.5" customHeight="1" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:6">
+      <c r="A11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" ht="40.5" customHeight="1" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>34</v>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" ht="39" customHeight="1" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>16</v>
+      <c r="A12" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>39</v>
@@ -3050,107 +3064,107 @@
         <v>19</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" ht="84" customHeight="1" spans="1:6">
+      <c r="A13" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" ht="100" customHeight="1" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" ht="100" customHeight="1" spans="1:6">
+      <c r="A14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="14" ht="69" customHeight="1" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="E14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="84" customHeight="1" spans="1:6">
+      <c r="A15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="C15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" ht="71" customHeight="1" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>16</v>
+      <c r="F15" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="78" customHeight="1" spans="1:6">
+      <c r="A16" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>44</v>
+        <v>19</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17" ht="130" customHeight="1" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
+      <c r="B17" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="C17" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>11</v>
@@ -3158,19 +3172,19 @@
     </row>
     <row r="18" ht="126" customHeight="1" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>11</v>
@@ -3178,19 +3192,19 @@
     </row>
     <row r="19" ht="120" customHeight="1" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>11</v>
@@ -3198,19 +3212,19 @@
     </row>
     <row r="20" ht="119" customHeight="1" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>11</v>
@@ -3218,59 +3232,59 @@
     </row>
     <row r="21" ht="117" customHeight="1" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="84" customHeight="1" spans="1:6">
       <c r="A22" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="128" customHeight="1" spans="1:6">
       <c r="A23" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="14" t="s">
         <v>67</v>
       </c>
+      <c r="C23" s="14" t="s">
+        <v>68</v>
+      </c>
       <c r="D23" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>11</v>
@@ -3278,79 +3292,79 @@
     </row>
     <row r="24" ht="132" customHeight="1" spans="1:6">
       <c r="A24" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" ht="128" customHeight="1" spans="1:6">
       <c r="A25" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" ht="189" customHeight="1" spans="1:6">
       <c r="A26" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="16" t="s">
         <v>76</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" ht="148.5" customHeight="1" spans="1:6">
       <c r="A27" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>11</v>
@@ -3358,19 +3372,19 @@
     </row>
     <row r="28" ht="134" customHeight="1" spans="1:6">
       <c r="A28" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>11</v>
@@ -3378,19 +3392,19 @@
     </row>
     <row r="29" ht="129" customHeight="1" spans="1:6">
       <c r="A29" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>11</v>
@@ -3398,59 +3412,59 @@
     </row>
     <row r="30" ht="148.5" customHeight="1" spans="1:6">
       <c r="A30" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="15" t="s">
         <v>88</v>
       </c>
+      <c r="C30" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="D30" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="31" ht="132" customHeight="1" spans="1:6">
       <c r="A31" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" ht="148.5" customHeight="1" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="15" t="s">
         <v>93</v>
       </c>
+      <c r="C32" s="14" t="s">
+        <v>94</v>
+      </c>
       <c r="D32" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>11</v>
@@ -3458,59 +3472,59 @@
     </row>
     <row r="33" ht="121.5" customHeight="1" spans="1:6">
       <c r="A33" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="15" t="s">
         <v>96</v>
       </c>
+      <c r="C33" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="D33" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" ht="121.5" customHeight="1" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>98</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="35" ht="148.5" customHeight="1" spans="1:6">
       <c r="A35" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>11</v>
@@ -3518,16 +3532,16 @@
     </row>
     <row r="36" ht="148.5" customHeight="1" spans="1:6">
       <c r="A36" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="15" t="s">
         <v>104</v>
       </c>
+      <c r="C36" s="14" t="s">
+        <v>105</v>
+      </c>
       <c r="D36" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>10</v>
@@ -3538,39 +3552,39 @@
     </row>
     <row r="37" ht="39" customHeight="1" spans="1:6">
       <c r="A37" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="15" t="s">
         <v>107</v>
       </c>
+      <c r="C37" s="14" t="s">
+        <v>108</v>
+      </c>
       <c r="D37" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" ht="148.5" customHeight="1" spans="1:6">
       <c r="A38" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>11</v>
@@ -3578,19 +3592,19 @@
     </row>
     <row r="39" ht="148.5" customHeight="1" spans="1:6">
       <c r="A39" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>113</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>11</v>
@@ -3598,79 +3612,79 @@
     </row>
     <row r="40" ht="63" customHeight="1" spans="1:6">
       <c r="A40" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="17" t="s">
         <v>117</v>
       </c>
+      <c r="C40" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="D40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" ht="108" customHeight="1" spans="1:6">
       <c r="A41" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" ht="135" customHeight="1" spans="1:6">
       <c r="A42" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C42" s="17" t="s">
         <v>123</v>
       </c>
+      <c r="C42" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="D42" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" ht="78" customHeight="1" spans="1:6">
       <c r="A43" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>21</v>
@@ -3678,19 +3692,19 @@
     </row>
     <row r="44" ht="77" customHeight="1" spans="1:6">
       <c r="A44" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>21</v>
@@ -3698,579 +3712,579 @@
     </row>
     <row r="45" ht="57" customHeight="1" spans="1:6">
       <c r="A45" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" ht="50" customHeight="1" spans="1:6">
       <c r="A46" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F46" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" ht="53" customHeight="1" spans="1:6">
+      <c r="A47" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="47" ht="53" customHeight="1" spans="1:6">
-      <c r="A47" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B47" s="5" t="s">
+      <c r="F47" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="48" ht="67" customHeight="1" spans="1:6">
       <c r="A48" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>144</v>
+        <v>84</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="49" ht="57" customHeight="1" spans="1:6">
       <c r="A49" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="50" ht="121.5" customHeight="1" spans="1:6">
       <c r="A50" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" ht="136" customHeight="1" spans="1:6">
       <c r="A51" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="52" ht="121.5" customHeight="1" spans="1:6">
-      <c r="A52" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C52" s="15" t="s">
+      <c r="A52" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="14" t="s">
         <v>154</v>
       </c>
+      <c r="C52" s="14" t="s">
+        <v>155</v>
+      </c>
       <c r="D52" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E52" s="15" t="s">
-        <v>155</v>
+      <c r="E52" s="14" t="s">
+        <v>156</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" ht="121.5" customHeight="1" spans="1:6">
-      <c r="A53" s="15" t="s">
-        <v>147</v>
+      <c r="A53" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" ht="121.5" customHeight="1" spans="1:6">
-      <c r="A54" s="15" t="s">
-        <v>147</v>
+      <c r="A54" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" ht="121.5" customHeight="1" spans="1:6">
-      <c r="A55" s="15" t="s">
-        <v>147</v>
+      <c r="A55" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" ht="121.5" customHeight="1" spans="1:6">
-      <c r="A56" s="15" t="s">
-        <v>147</v>
+      <c r="A56" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" ht="105" customHeight="1" spans="1:6">
-      <c r="A57" s="15" t="s">
-        <v>147</v>
+      <c r="A57" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" ht="121.5" customHeight="1" spans="1:6">
-      <c r="A58" s="15" t="s">
-        <v>147</v>
+      <c r="A58" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" ht="33" customHeight="1" spans="1:6">
       <c r="A59" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" ht="29" customHeight="1" spans="1:6">
       <c r="A60" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" ht="40.5" customHeight="1" spans="1:6">
       <c r="A61" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F61" s="12" t="s">
         <v>175</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="62" ht="40.5" customHeight="1" spans="1:6">
       <c r="A62" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" ht="40.5" customHeight="1" spans="1:6">
       <c r="A63" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>180</v>
-      </c>
       <c r="F63" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" ht="29" customHeight="1" spans="1:6">
       <c r="A64" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" ht="40.5" customHeight="1" spans="1:6">
       <c r="A65" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" ht="35" customHeight="1" spans="1:6">
       <c r="A66" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>188</v>
+        <v>169</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" ht="67" customHeight="1" spans="1:6">
       <c r="A67" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" ht="69" customHeight="1" spans="1:6">
       <c r="A68" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F68" s="12" t="s">
         <v>196</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="69" ht="63" customHeight="1" spans="1:6">
       <c r="A69" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" ht="54" customHeight="1" spans="1:6">
       <c r="A70" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" ht="54" customHeight="1" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" ht="54" customHeight="1" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" ht="67.5" customHeight="1" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>21</v>
@@ -4278,19 +4292,19 @@
     </row>
     <row r="74" ht="67.5" customHeight="1" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>21</v>
@@ -4298,19 +4312,19 @@
     </row>
     <row r="75" ht="67.5" customHeight="1" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>21</v>
@@ -4318,19 +4332,19 @@
     </row>
     <row r="76" ht="67.5" customHeight="1" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>21</v>
@@ -4338,19 +4352,19 @@
     </row>
     <row r="77" ht="67.5" customHeight="1" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>21</v>
@@ -4358,19 +4372,19 @@
     </row>
     <row r="78" ht="67.5" customHeight="1" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>21</v>
@@ -4378,19 +4392,19 @@
     </row>
     <row r="79" ht="67.5" customHeight="1" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>21</v>
@@ -4398,19 +4412,19 @@
     </row>
     <row r="80" ht="67.5" customHeight="1" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F80" s="12" t="s">
         <v>21</v>
@@ -4418,19 +4432,19 @@
     </row>
     <row r="81" ht="67.5" customHeight="1" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>21</v>
@@ -4438,19 +4452,19 @@
     </row>
     <row r="82" ht="67.5" customHeight="1" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>21</v>
@@ -4458,19 +4472,19 @@
     </row>
     <row r="83" ht="75" customHeight="1" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>21</v>
@@ -4478,19 +4492,19 @@
     </row>
     <row r="84" ht="67.5" customHeight="1" spans="1:6">
       <c r="A84" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>21</v>
@@ -4498,19 +4512,19 @@
     </row>
     <row r="85" ht="67.5" customHeight="1" spans="1:6">
       <c r="A85" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F85" s="12" t="s">
         <v>21</v>
@@ -4518,19 +4532,19 @@
     </row>
     <row r="86" ht="67.5" customHeight="1" spans="1:6">
       <c r="A86" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>21</v>
@@ -4538,19 +4552,19 @@
     </row>
     <row r="87" ht="67.5" customHeight="1" spans="1:6">
       <c r="A87" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>21</v>
@@ -4558,19 +4572,19 @@
     </row>
     <row r="88" ht="67.5" customHeight="1" spans="1:6">
       <c r="A88" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>21</v>
@@ -4578,19 +4592,19 @@
     </row>
     <row r="89" ht="67.5" customHeight="1" spans="1:6">
       <c r="A89" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F89" s="12" t="s">
         <v>21</v>
@@ -4598,19 +4612,19 @@
     </row>
     <row r="90" ht="67.5" customHeight="1" spans="1:6">
       <c r="A90" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F90" s="12" t="s">
         <v>21</v>
@@ -4618,19 +4632,19 @@
     </row>
     <row r="91" ht="75" customHeight="1" spans="1:6">
       <c r="A91" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F91" s="12" t="s">
         <v>21</v>
@@ -4638,1995 +4652,1995 @@
     </row>
     <row r="92" ht="78" customHeight="1" spans="1:6">
       <c r="A92" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B92" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="B92" s="14" t="s">
         <v>246</v>
       </c>
+      <c r="C92" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="D92" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" ht="67.5" customHeight="1" spans="1:6">
       <c r="A93" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B93" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F93" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="94" ht="67.5" customHeight="1" spans="1:6">
       <c r="A94" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E94" s="15" t="s">
-        <v>253</v>
+      <c r="E94" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" ht="67.5" customHeight="1" spans="1:6">
       <c r="A95" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F95" s="12" t="s">
         <v>255</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="96" ht="67.5" customHeight="1" spans="1:6">
       <c r="A96" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B96" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>257</v>
-      </c>
       <c r="F96" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" ht="67.5" customHeight="1" spans="1:6">
       <c r="A97" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" ht="67.5" customHeight="1" spans="1:6">
       <c r="A98" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99" ht="63" customHeight="1" spans="1:6">
       <c r="A99" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" ht="63" customHeight="1" spans="1:6">
       <c r="A100" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B100" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F100" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F100" s="12" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="101" ht="69" customHeight="1" spans="1:6">
       <c r="A101" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" ht="121.5" customHeight="1" spans="1:6">
       <c r="A102" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F102" s="15" t="s">
-        <v>150</v>
+        <v>114</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="103" ht="121.5" customHeight="1" spans="1:6">
       <c r="A103" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="F103" s="15" t="s">
-        <v>150</v>
+        <v>278</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="104" ht="121.5" customHeight="1" spans="1:6">
       <c r="A104" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F104" s="15" t="s">
-        <v>150</v>
+        <v>114</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="105" ht="27" customHeight="1" spans="1:6">
       <c r="A105" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" ht="27" customHeight="1" spans="1:6">
       <c r="A106" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F106" s="6"/>
     </row>
     <row r="107" ht="27" customHeight="1" spans="1:6">
       <c r="A107" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F107" s="6"/>
     </row>
     <row r="108" ht="27" customHeight="1" spans="1:6">
       <c r="A108" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F108" s="6"/>
     </row>
     <row r="109" ht="27" customHeight="1" spans="1:6">
       <c r="A109" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F109" s="6"/>
     </row>
     <row r="110" ht="27" customHeight="1" spans="1:6">
       <c r="A110" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F110" s="6"/>
     </row>
     <row r="111" ht="27" customHeight="1" spans="1:6">
       <c r="A111" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F111" s="6"/>
     </row>
     <row r="112" ht="27" customHeight="1" spans="1:6">
       <c r="A112" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F112" s="6"/>
     </row>
     <row r="113" ht="27" customHeight="1" spans="1:6">
       <c r="A113" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F113" s="6"/>
     </row>
     <row r="114" ht="27" customHeight="1" spans="1:6">
       <c r="A114" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F114" s="6"/>
     </row>
     <row r="115" ht="27" customHeight="1" spans="1:6">
       <c r="A115" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F115" s="6"/>
     </row>
     <row r="116" ht="40.5" customHeight="1" spans="1:6">
       <c r="A116" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F116" s="6"/>
     </row>
     <row r="117" ht="40.5" customHeight="1" spans="1:6">
       <c r="A117" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F117" s="6"/>
     </row>
     <row r="118" ht="40.5" customHeight="1" spans="1:6">
       <c r="A118" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F118" s="6"/>
     </row>
     <row r="119" ht="40.5" customHeight="1" spans="1:6">
       <c r="A119" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F119" s="6"/>
     </row>
     <row r="120" ht="27" customHeight="1" spans="1:6">
       <c r="A120" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F120" s="6"/>
     </row>
     <row r="121" ht="40.5" customHeight="1" spans="1:6">
       <c r="A121" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F121" s="6"/>
     </row>
     <row r="122" ht="27" customHeight="1" spans="1:6">
       <c r="A122" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F122" s="6"/>
     </row>
     <row r="123" ht="40.5" customHeight="1" spans="1:6">
       <c r="A123" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F123" s="6"/>
     </row>
     <row r="124" ht="27" customHeight="1" spans="1:6">
       <c r="A124" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F124" s="6"/>
     </row>
     <row r="125" ht="27" customHeight="1" spans="1:6">
       <c r="A125" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F125" s="6"/>
     </row>
     <row r="126" ht="27" customHeight="1" spans="1:6">
       <c r="A126" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F126" s="6"/>
     </row>
     <row r="127" ht="27" customHeight="1" spans="1:6">
       <c r="A127" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F127" s="6"/>
     </row>
     <row r="128" ht="27" customHeight="1" spans="1:6">
       <c r="A128" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F128" s="6"/>
     </row>
     <row r="129" ht="27" customHeight="1" spans="1:6">
       <c r="A129" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F129" s="6"/>
     </row>
     <row r="130" ht="27" customHeight="1" spans="1:6">
       <c r="A130" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F130" s="6"/>
     </row>
     <row r="131" ht="27" customHeight="1" spans="1:6">
       <c r="A131" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F131" s="6"/>
     </row>
     <row r="132" ht="27" customHeight="1" spans="1:6">
       <c r="A132" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F132" s="6"/>
     </row>
     <row r="133" ht="27" customHeight="1" spans="1:6">
       <c r="A133" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F133" s="6"/>
     </row>
     <row r="134" ht="27" customHeight="1" spans="1:6">
       <c r="A134" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F134" s="6"/>
     </row>
     <row r="135" ht="27" customHeight="1" spans="1:6">
       <c r="A135" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F135" s="6"/>
     </row>
     <row r="136" ht="27" customHeight="1" spans="1:6">
       <c r="A136" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F136" s="6"/>
     </row>
     <row r="137" ht="27" customHeight="1" spans="1:6">
       <c r="A137" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F137" s="6"/>
     </row>
     <row r="138" ht="27" customHeight="1" spans="1:6">
       <c r="A138" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F138" s="6"/>
     </row>
     <row r="139" ht="40.5" customHeight="1" spans="1:6">
       <c r="A139" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F139" s="6"/>
     </row>
     <row r="140" ht="27" customHeight="1" spans="1:6">
       <c r="A140" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F140" s="6"/>
     </row>
     <row r="141" ht="27" customHeight="1" spans="1:6">
       <c r="A141" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F141" s="6"/>
     </row>
     <row r="142" ht="27" customHeight="1" spans="1:6">
       <c r="A142" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F142" s="6"/>
     </row>
     <row r="143" ht="27" customHeight="1" spans="1:6">
       <c r="A143" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F143" s="6"/>
     </row>
     <row r="144" ht="27" customHeight="1" spans="1:6">
       <c r="A144" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F144" s="6"/>
     </row>
     <row r="145" ht="27" customHeight="1" spans="1:6">
       <c r="A145" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F145" s="6"/>
     </row>
     <row r="146" ht="27" customHeight="1" spans="1:6">
       <c r="A146" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F146" s="6"/>
     </row>
     <row r="147" ht="27" customHeight="1" spans="1:6">
       <c r="A147" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F147" s="6"/>
     </row>
     <row r="148" ht="27" customHeight="1" spans="1:6">
       <c r="A148" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F148" s="6"/>
     </row>
     <row r="149" ht="27" customHeight="1" spans="1:6">
       <c r="A149" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F149" s="6"/>
     </row>
     <row r="150" ht="27" customHeight="1" spans="1:6">
       <c r="A150" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F150" s="6"/>
     </row>
     <row r="151" ht="27" customHeight="1" spans="1:6">
       <c r="A151" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F151" s="6"/>
     </row>
     <row r="152" ht="27" customHeight="1" spans="1:6">
       <c r="A152" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F152" s="8"/>
+        <v>53</v>
+      </c>
+      <c r="F152" s="7"/>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F153" s="12" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F154" s="6"/>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F155" s="6"/>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F156" s="6"/>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F157" s="6"/>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F158" s="6"/>
     </row>
-    <row r="159" ht="30" spans="1:6">
+    <row r="159" spans="1:6">
       <c r="A159" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F159" s="6"/>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F160" s="6"/>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F161" s="6"/>
     </row>
-    <row r="162" ht="30" spans="1:6">
+    <row r="162" ht="28.8" spans="1:6">
       <c r="A162" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F162" s="6"/>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F163" s="6"/>
     </row>
     <row r="164" ht="40.5" customHeight="1" spans="1:6">
       <c r="A164" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F164" s="6"/>
     </row>
     <row r="165" ht="27" customHeight="1" spans="1:6">
       <c r="A165" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F165" s="6"/>
     </row>
     <row r="166" ht="27" customHeight="1" spans="1:6">
       <c r="A166" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F166" s="6"/>
     </row>
     <row r="167" ht="27" customHeight="1" spans="1:6">
       <c r="A167" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F167" s="6"/>
     </row>
     <row r="168" ht="27" customHeight="1" spans="1:6">
       <c r="A168" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F168" s="6"/>
     </row>
     <row r="169" ht="27" customHeight="1" spans="1:6">
       <c r="A169" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F169" s="6"/>
     </row>
     <row r="170" ht="27" customHeight="1" spans="1:6">
       <c r="A170" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F170" s="6"/>
     </row>
     <row r="171" ht="27" customHeight="1" spans="1:6">
       <c r="A171" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F171" s="6"/>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F172" s="6"/>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F173" s="6"/>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F174" s="6"/>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F175" s="6"/>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F176" s="6"/>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F177" s="6"/>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F178" s="6"/>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F179" s="6"/>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F180" s="6"/>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F181" s="6"/>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F182" s="6"/>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F183" s="6"/>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F184" s="6"/>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" ht="28.8" spans="1:6">
       <c r="A185" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F185" s="6"/>
     </row>
     <row r="186" ht="27" customHeight="1" spans="1:6">
       <c r="A186" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F186" s="6"/>
     </row>
     <row r="187" ht="27" customHeight="1" spans="1:6">
       <c r="A187" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F187" s="6"/>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F188" s="6"/>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F189" s="6"/>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F190" s="6"/>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F191" s="6"/>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F192" s="6"/>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F193" s="6"/>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F194" s="6"/>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F195" s="6"/>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F196" s="6"/>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F197" s="6"/>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F198" s="6"/>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F199" s="6"/>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F200" s="8"/>
+        <v>53</v>
+      </c>
+      <c r="F200" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6643,633 +6657,633 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6296296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="6"/>
       <c r="B3" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="60" customHeight="1" spans="1:3">
       <c r="A4" s="6"/>
-      <c r="B4" s="7" t="s">
-        <v>480</v>
+      <c r="B4" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="6"/>
       <c r="B5" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="6"/>
       <c r="B6" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="7"/>
       <c r="B8" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="6"/>
       <c r="B10" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="6"/>
       <c r="B11" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="54" customHeight="1" spans="1:3">
       <c r="A12" s="6"/>
-      <c r="B12" s="7" t="s">
-        <v>480</v>
+      <c r="B12" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="27" customHeight="1" spans="1:3">
       <c r="A13" s="6"/>
       <c r="B13" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="6"/>
       <c r="B14" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="27" customHeight="1" spans="1:3">
       <c r="A15" s="6"/>
       <c r="B15" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="6"/>
       <c r="B16" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="6"/>
       <c r="B20" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="54" customHeight="1" spans="1:3">
       <c r="A21" s="6"/>
-      <c r="B21" s="7" t="s">
-        <v>480</v>
+      <c r="B21" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="6"/>
       <c r="B23" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="6"/>
       <c r="B24" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
-      <c r="A25" s="8"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="6"/>
       <c r="B27" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="54" customHeight="1" spans="1:3">
       <c r="A28" s="6"/>
-      <c r="B28" s="7" t="s">
-        <v>480</v>
+      <c r="B28" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="6"/>
       <c r="B30" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="6"/>
       <c r="B31" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="6"/>
       <c r="B32" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9" t="s">
-        <v>498</v>
+      <c r="A33" s="7"/>
+      <c r="B33" s="8" t="s">
+        <v>499</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="6"/>
       <c r="B35" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="6"/>
       <c r="B36" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="6"/>
       <c r="B37" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="54" customHeight="1" spans="1:3">
       <c r="A38" s="6"/>
-      <c r="B38" s="7" t="s">
-        <v>480</v>
+      <c r="B38" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="6"/>
       <c r="B39" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="6"/>
       <c r="B40" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="6"/>
       <c r="B41" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
-      <c r="A42" s="8"/>
+      <c r="A42" s="7"/>
       <c r="B42" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="6"/>
       <c r="B44" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="54" customHeight="1" spans="1:3">
       <c r="A45" s="6"/>
-      <c r="B45" s="7" t="s">
-        <v>480</v>
+      <c r="B45" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="6"/>
       <c r="B46" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="6"/>
       <c r="B47" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="6"/>
       <c r="B48" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="6"/>
       <c r="B49" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
-      <c r="A50" s="8"/>
+      <c r="A50" s="7"/>
       <c r="B50" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="6"/>
       <c r="B52" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="54" customHeight="1" spans="1:3">
       <c r="A53" s="6"/>
-      <c r="B53" s="7" t="s">
-        <v>480</v>
+      <c r="B53" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="6"/>
       <c r="B54" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="6"/>
       <c r="B55" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="6"/>
       <c r="B56" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="6"/>
       <c r="B57" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
-      <c r="A58" s="8"/>
+      <c r="A58" s="7"/>
       <c r="B58" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="6"/>
       <c r="B60" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="61" ht="54" customHeight="1" spans="1:3">
       <c r="A61" s="6"/>
-      <c r="B61" s="7" t="s">
-        <v>480</v>
+      <c r="B61" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="6"/>
       <c r="B62" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="6"/>
       <c r="B63" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="6"/>
       <c r="B64" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="6"/>
       <c r="B65" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="6"/>
       <c r="B66" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="8"/>
+      <c r="A67" s="7"/>
       <c r="B67" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -978,7 +978,8 @@
     <t>Atlas 850E 超节点
 Atlas 850 超节点
 Atlas 650E 服务器
-Atlas 650 服务器</t>
+Atlas 650 服务器
+Atlas 950 SuperPoD Flex</t>
   </si>
   <si>
     <t>npu_chip_info_optical_tx_power_Z</t>
